--- a/Input/Names_variations.xlsx
+++ b/Input/Names_variations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7543F231-DFEE-4BC9-A34C-746E1180B159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57CE109-E025-4EDC-B308-38F8124331AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Devendra Fadnavis" sheetId="1" r:id="rId1"/>

--- a/Input/Names_variations.xlsx
+++ b/Input/Names_variations.xlsx
@@ -8,20 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9928065-8F3A-48F0-8E89-A94C64E61468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD479C2C-0E83-4C41-A477-BEF3ACED201B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Devendra Fadnavis" sheetId="1" r:id="rId1"/>
-    <sheet name="Eknath Shinde" sheetId="2" r:id="rId2"/>
-    <sheet name="Chandrakant Patil" sheetId="3" r:id="rId3"/>
-    <sheet name="Ashish Shelar" sheetId="4" r:id="rId4"/>
-    <sheet name="Ravindra Chavan" sheetId="5" r:id="rId5"/>
-    <sheet name="Prakash Abitkar" sheetId="6" r:id="rId6"/>
-    <sheet name="Chandrashekhar Bawankule" sheetId="7" r:id="rId7"/>
-    <sheet name="Shivraj Singh Chauhan" sheetId="10" r:id="rId8"/>
+    <sheet name="Jaykumar Gore" sheetId="11" r:id="rId2"/>
+    <sheet name="Eknath Shinde" sheetId="2" r:id="rId3"/>
+    <sheet name="Chandrakant Patil" sheetId="3" r:id="rId4"/>
+    <sheet name="Ashish Shelar" sheetId="4" r:id="rId5"/>
+    <sheet name="Ravindra Chavan" sheetId="5" r:id="rId6"/>
+    <sheet name="Prakash Abitkar" sheetId="6" r:id="rId7"/>
+    <sheet name="Chandrashekhar Bawankule" sheetId="7" r:id="rId8"/>
+    <sheet name="Shivraj Singh Chauhan" sheetId="10" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Jaykumar Gore'!$A$1:$B$9</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -32,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="191">
   <si>
     <t>English</t>
   </si>
@@ -557,13 +561,61 @@
   </si>
   <si>
     <t>शिवराज सिंह चव्हान</t>
+  </si>
+  <si>
+    <t>Jaykumar Gore</t>
+  </si>
+  <si>
+    <t>Jaykumar</t>
+  </si>
+  <si>
+    <t>Gore</t>
+  </si>
+  <si>
+    <t>Jay</t>
+  </si>
+  <si>
+    <t>Jay Bhau</t>
+  </si>
+  <si>
+    <t>Gore Saheb</t>
+  </si>
+  <si>
+    <t>MLA Jaykumar Gore</t>
+  </si>
+  <si>
+    <t>Jaykumar Bhagwanrao Gore</t>
+  </si>
+  <si>
+    <t>जयकुमार गोरे</t>
+  </si>
+  <si>
+    <t>जयकुमार</t>
+  </si>
+  <si>
+    <t>गोरे</t>
+  </si>
+  <si>
+    <t>जय</t>
+  </si>
+  <si>
+    <t>जय भाऊ</t>
+  </si>
+  <si>
+    <t>गोरे साहेब</t>
+  </si>
+  <si>
+    <t>आमदार जयकुमार गोरे</t>
+  </si>
+  <si>
+    <t>जयकुमार भगवानराव गोरे</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -587,6 +639,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1B1C1D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FF1B1C1D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -608,7 +673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -616,6 +681,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1010,6 +1081,88 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6D654C-BA22-496E-9704-7C8B5444653B}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CA14A4-B9BE-4C0F-A6C7-8694C2FEB2FD}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1123,7 +1276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C49115B-22BA-4B1C-82AA-297931751286}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1237,7 +1390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D432222D-172F-4700-B536-AEC3702AB6E7}">
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1359,7 +1512,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FD54DAC-939D-44B0-8E6D-C38E1312A5DD}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1477,7 +1630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB8E8C3-42ED-4F61-9434-E5F50CFD09B4}">
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1599,7 +1752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632DF8DE-5846-4F34-B6FB-D1EF0D496859}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1715,7 +1868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C80E34BD-CC9C-49E6-BDBB-0653D3E6BE3A}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
